--- a/AAII_Financials/Quarterly/AUNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AUNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>AUNA</t>
   </si>
@@ -656,264 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>362600</v>
+      </c>
+      <c r="E8" s="3">
         <v>337300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>336600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>322200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>309000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>284200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>281800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>303000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>292200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>289300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>274900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>268300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>260700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>237700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>158300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>278500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>382800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>167600</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>233100</v>
+      </c>
+      <c r="E9" s="3">
         <v>213800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>209200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>201300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>186300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>180100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>166700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>182100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>180800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>177900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>173700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>170000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>161600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>150500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>176800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>242400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>129500</v>
+      </c>
+      <c r="E10" s="3">
         <v>123500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>127400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>120900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>122700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>104100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>115100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>120800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>111500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>111400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>101200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>98300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>99100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>87200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>57700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>101600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>140400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +947,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -990,8 +1004,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,44 +1063,47 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>18700</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>36000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1102,64 +1122,70 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E15" s="3">
         <v>14400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1203,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>315100</v>
+      </c>
+      <c r="E17" s="3">
         <v>293000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>294400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>274400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>259200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>246300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>231400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>241400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>244600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>240400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>234900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>228800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>223300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>199200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>140900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>252200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>351400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E18" s="3">
         <v>44400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>42200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>49800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>61600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>48900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>40000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>31400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,288 +1344,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>24600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>26300</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="L20" s="3">
+        <v>15100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O20" s="3">
+        <v>11300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="U20" s="3">
         <v>-14200</v>
       </c>
-      <c r="H20" s="3">
-        <v>-10900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>26300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>15100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>4300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>11300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-19800</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-14200</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E21" s="3">
         <v>51900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>73200</v>
       </c>
-      <c r="G21" s="3">
-        <v>77600</v>
-      </c>
       <c r="H21" s="3">
+        <v>83500</v>
+      </c>
+      <c r="I21" s="3">
         <v>61500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>81000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>45400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>63600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>45400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>60000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>57900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E22" s="3">
         <v>33900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>32100</v>
       </c>
-      <c r="G22" s="3">
-        <v>28100</v>
-      </c>
       <c r="H22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I22" s="3">
         <v>33600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>33100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>34400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>35900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E23" s="3">
         <v>4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-45700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1696,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-59100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6200</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-56900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1873,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1932,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1991,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2050,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-24600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="K32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>9600</v>
+      </c>
+      <c r="T32" s="3">
+        <v>19800</v>
+      </c>
+      <c r="U32" s="3">
         <v>14200</v>
       </c>
-      <c r="H32" s="3">
-        <v>10900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-26300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>6600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>8700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>3800</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>11000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>9600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>19800</v>
-      </c>
-      <c r="T32" s="3">
-        <v>14200</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-56900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2227,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-56900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2375,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,53 +2398,54 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E41" s="3">
         <v>117000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>65100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>64900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>89100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2368,53 +2455,56 @@
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>28800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>25100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>18800</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
@@ -2424,53 +2514,56 @@
       <c r="T42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>335300</v>
+      </c>
+      <c r="E43" s="3">
         <v>324100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>313800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>310300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>287500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>277600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>255000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>264600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>254600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>253000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>231800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>217100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>201800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>187900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2480,53 +2573,56 @@
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E44" s="3">
         <v>45600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>49000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>42900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>39300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>38100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>32100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>34000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>35100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>27500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>25400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>25300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2536,53 +2632,56 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E45" s="3">
         <v>80500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>76800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>73800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>76800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>71800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>69500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>58300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>60300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>60200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>57300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>80700</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2592,53 +2691,56 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>597900</v>
+      </c>
+      <c r="E46" s="3">
         <v>573100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>548300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>520900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>484600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>463800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>451800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>439000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>414900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>448600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>417200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>413800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>366900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>383200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2648,53 +2750,56 @@
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E47" s="3">
         <v>9200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>5600</v>
       </c>
       <c r="M47" s="3">
         <v>5600</v>
       </c>
       <c r="N47" s="3">
-        <v>5100</v>
+        <v>5600</v>
       </c>
       <c r="O47" s="3">
         <v>5100</v>
       </c>
       <c r="P47" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q47" s="3">
         <v>4300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2704,53 +2809,56 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>734300</v>
+      </c>
+      <c r="E48" s="3">
         <v>708400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>713400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>698000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>685100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>655500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>639300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>659700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>677400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>734200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>730400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>702900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>712200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>671800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2760,53 +2868,56 @@
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>836100</v>
+      </c>
+      <c r="E49" s="3">
         <v>807000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>803900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>788500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>768500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>721800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>704400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>737600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>778200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>855700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>842700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>816600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>824700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>775600</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2816,8 +2927,11 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2986,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,53 +3045,56 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E52" s="3">
         <v>28600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8900</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2984,8 +3104,11 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,53 +3163,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2282900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2202200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2169300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2100300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2024700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1928800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1877400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1922600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1954100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2123900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2070700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2023300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1980900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1882200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3096,8 +3222,11 @@
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3247,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,53 +3270,54 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E57" s="3">
         <v>314300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>291100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>272800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>238700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>248400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>228300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>232800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>219900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>216500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>189400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>153000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>151700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>146800</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3196,53 +3327,56 @@
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E58" s="3">
         <v>131200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>115300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>209800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>186400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>224100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>194200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>164700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>142900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>132100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>129900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>135200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>112800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>603800</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3252,53 +3386,56 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E59" s="3">
         <v>80600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>92800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>82900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>101700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>142600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>157100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>94600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>133400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>116300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>115700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3308,53 +3445,56 @@
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>555800</v>
+      </c>
+      <c r="E60" s="3">
         <v>526200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>495500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>580900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>531800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>555500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>515800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>499200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>505400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>505600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>454900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>431900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>390800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>866300</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3364,53 +3504,56 @@
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>975300</v>
+      </c>
+      <c r="E61" s="3">
         <v>976900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1033200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>905900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>898600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>835800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>838700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>861500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>915200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1009800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1000800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>880000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>869700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>377400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3420,53 +3563,56 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E62" s="3">
         <v>66300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1100</v>
       </c>
       <c r="M62" s="3">
         <v>1100</v>
       </c>
       <c r="N62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O62" s="3">
         <v>64500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>66100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>77400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3476,8 +3622,11 @@
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3681,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3740,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,53 +3799,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1682000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1652700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1644300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1576800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1517300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1472900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1447100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1473700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1527700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1640100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1592300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1514800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1469800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1454900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3700,8 +3858,11 @@
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3883,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3940,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3999,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4058,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,53 +4117,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-53300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-57300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-31200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-65000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-72500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-75900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-102100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-98800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-40300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-38600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4002,8 +4176,11 @@
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4235,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4294,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,53 +4353,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>544500</v>
+      </c>
+      <c r="E76" s="3">
         <v>498000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>475800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>478100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>464200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>414300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>391700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>408500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>386000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>441100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>394600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>426500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>353600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>298900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4226,8 +4412,11 @@
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4471,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-56900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,64 +4619,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
         <v>9600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>9900</v>
       </c>
       <c r="I83" s="3">
         <v>9900</v>
       </c>
       <c r="J83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K83" s="3">
         <v>10500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4735,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4794,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4853,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4912,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4971,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E89" s="3">
         <v>50100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>66200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>54400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>54700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>41500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>39300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>41400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,64 +5055,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-8700</v>
       </c>
       <c r="I91" s="3">
         <v>-8700</v>
       </c>
       <c r="J91" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-6200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-35000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-84000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-74300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5171,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5230,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-148100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-33400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13900</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5314,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5125,8 +5359,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5137,8 +5371,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5430,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5489,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,99 +5548,105 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-44900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-36700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-37000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-45100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-50500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>149400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>72300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-500</v>
       </c>
       <c r="O101" s="3">
         <v>-500</v>
@@ -5406,71 +5655,77 @@
         <v>-500</v>
       </c>
       <c r="Q101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E102" s="3">
         <v>21000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>81500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10300</v>
       </c>
     </row>
